--- a/single-api/amazon-dsp-api/swagger_modules.xlsx
+++ b/single-api/amazon-dsp-api/swagger_modules.xlsx
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,6 +95,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -515,6 +518,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -547,6 +555,11 @@
           <t>3% (1/30)</t>
         </is>
       </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ABTest</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -579,6 +592,11 @@
           <t>60% (18/30)</t>
         </is>
       </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ABTestV2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -611,6 +629,11 @@
           <t>0% (0/4)</t>
         </is>
       </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Account</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -643,6 +666,11 @@
           <t>67% (2/3)</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Advertiser</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -675,6 +703,11 @@
           <t>94% (15/16)</t>
         </is>
       </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -707,6 +740,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Alert</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -739,6 +777,11 @@
           <t>79% (11/14)</t>
         </is>
       </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcAgent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -771,6 +814,11 @@
           <t>76% (13/17)</t>
         </is>
       </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcAudience</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -803,6 +851,11 @@
           <t>88% (29/33)</t>
         </is>
       </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcAudienceSolution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -835,6 +888,11 @@
           <t>78% (29/37)</t>
         </is>
       </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcExploration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -867,6 +925,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcOAuth2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -899,6 +962,11 @@
           <t>84% (132/157)</t>
         </is>
       </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcReport</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -931,6 +999,11 @@
           <t>90% (53/59)</t>
         </is>
       </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AmcReportV2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -963,6 +1036,11 @@
           <t>17% (1/6)</t>
         </is>
       </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AsyncTask</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -995,6 +1073,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AsyncTaskV2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1027,6 +1110,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AttachFile</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1059,6 +1147,11 @@
           <t>69% (22/32)</t>
         </is>
       </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Audience</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1091,6 +1184,11 @@
           <t>8% (2/26)</t>
         </is>
       </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Audit</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1123,6 +1221,11 @@
           <t>88% (15/17)</t>
         </is>
       </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\AuditV2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1155,6 +1258,11 @@
           <t>83% (5/6)</t>
         </is>
       </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\BatchProcessing</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1187,6 +1295,11 @@
           <t>43% (3/7)</t>
         </is>
       </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\BidModifier</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1219,6 +1332,11 @@
           <t>89% (8/9)</t>
         </is>
       </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\BidModifierV2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1251,6 +1369,11 @@
           <t>35% (6/17)</t>
         </is>
       </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Budget</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1283,6 +1406,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Commitment</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1315,6 +1443,11 @@
           <t>36% (4/11)</t>
         </is>
       </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Conversion</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1347,6 +1480,11 @@
           <t>52% (12/23)</t>
         </is>
       </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Copilot</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1379,6 +1517,11 @@
           <t>17% (12/69)</t>
         </is>
       </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Creative</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1411,6 +1554,11 @@
           <t>83% (19/23)</t>
         </is>
       </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\CreativeV2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1443,6 +1591,11 @@
           <t>33% (2/6)</t>
         </is>
       </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1475,6 +1628,11 @@
           <t>67% (37/55)</t>
         </is>
       </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DashboardV2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1507,6 +1665,11 @@
           <t>79% (19/24)</t>
         </is>
       </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Deal</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1539,6 +1702,11 @@
           <t>75% (12/16)</t>
         </is>
       </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DealV2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1571,6 +1739,11 @@
           <t>89% (16/18)</t>
         </is>
       </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DiscoveryV2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1603,6 +1776,11 @@
           <t>67% (2/3)</t>
         </is>
       </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Download</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1635,6 +1813,11 @@
           <t>86% (36/42)</t>
         </is>
       </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DownloadCenter</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1667,6 +1850,11 @@
           <t>30% (14/46)</t>
         </is>
       </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DSP</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1699,6 +1887,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DspOAuth2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1731,6 +1924,11 @@
           <t>88% (43/49)</t>
         </is>
       </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\DSPV2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1763,6 +1961,11 @@
           <t>38% (3/8)</t>
         </is>
       </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Event</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1795,6 +1998,11 @@
           <t>55% (6/11)</t>
         </is>
       </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\FusionReport</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1827,6 +2035,11 @@
           <t>0% (0/16)</t>
         </is>
       </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\HourlyData</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1859,6 +2072,11 @@
           <t>0% (0/8)</t>
         </is>
       </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\HTen</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1891,6 +2109,11 @@
           <t>100% (21/21)</t>
         </is>
       </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Itsumo</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1923,6 +2146,11 @@
           <t>47% (27/58)</t>
         </is>
       </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\LineItem</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1955,6 +2183,11 @@
           <t>92% (23/25)</t>
         </is>
       </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\LineItemV2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1987,6 +2220,11 @@
           <t>57% (4/7)</t>
         </is>
       </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\LocationIndex</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2019,6 +2257,11 @@
           <t>0% (0/3)</t>
         </is>
       </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\MSAccount</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2051,6 +2294,11 @@
           <t>77% (20/26)</t>
         </is>
       </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\MyReport</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2083,6 +2331,11 @@
           <t>68% (21/31)</t>
         </is>
       </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Order</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2115,6 +2368,11 @@
           <t>82% (9/11)</t>
         </is>
       </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\OrderV2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2147,6 +2405,11 @@
           <t>0% (0/12)</t>
         </is>
       </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\PerfReport</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2179,6 +2442,11 @@
           <t>0% (0/5)</t>
         </is>
       </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Persona</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2211,6 +2479,11 @@
           <t>92% (11/12)</t>
         </is>
       </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\PersonaAudienceInsight</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2243,6 +2516,11 @@
           <t>64% (7/11)</t>
         </is>
       </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Product</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2275,6 +2553,11 @@
           <t>55% (12/22)</t>
         </is>
       </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ProductV2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2307,6 +2590,11 @@
           <t>50% (1/2)</t>
         </is>
       </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Profile</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2339,6 +2627,11 @@
           <t>4% (2/56)</t>
         </is>
       </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Report</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2371,6 +2664,11 @@
           <t>75% (3/4)</t>
         </is>
       </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ReportMcp</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2403,6 +2701,11 @@
           <t>64% (37/58)</t>
         </is>
       </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ReportV2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2435,6 +2738,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Research</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2467,6 +2775,11 @@
           <t>4% (2/49)</t>
         </is>
       </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Rule</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2499,6 +2812,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\S3Test</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2531,6 +2849,11 @@
           <t>50% (11/22)</t>
         </is>
       </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\ShareLink</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2563,6 +2886,11 @@
           <t>31% (8/26)</t>
         </is>
       </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SuperWizard</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2595,6 +2923,11 @@
           <t>0% (0/7)</t>
         </is>
       </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SuperWizardV2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2627,6 +2960,11 @@
           <t>86% (12/14)</t>
         </is>
       </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SuperWizardV3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2659,6 +2997,11 @@
           <t>0% (0/7)</t>
         </is>
       </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Sync</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2691,6 +3034,11 @@
           <t>0% (0/28)</t>
         </is>
       </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SyncCK</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2723,6 +3071,11 @@
           <t>0% (0/2)</t>
         </is>
       </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SyncManual</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2755,6 +3108,11 @@
           <t>0% (0/7)</t>
         </is>
       </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\SyncV2</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2787,6 +3145,11 @@
           <t>46% (6/13)</t>
         </is>
       </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Tagging</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2819,6 +3182,11 @@
           <t>79% (27/34)</t>
         </is>
       </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\TaggingV2</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2851,6 +3219,11 @@
           <t>50% (1/2)</t>
         </is>
       </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Target</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2883,6 +3256,11 @@
           <t>44% (4/9)</t>
         </is>
       </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Template</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2915,6 +3293,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\TemplateV2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2947,6 +3330,11 @@
           <t>0% (0/26)</t>
         </is>
       </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\Test</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2979,6 +3367,11 @@
           <t>0% (0/3)</t>
         </is>
       </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\User</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3011,6 +3404,11 @@
           <t>50% (1/2)</t>
         </is>
       </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\UserV2</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3043,6 +3441,11 @@
           <t>0% (0/14)</t>
         </is>
       </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\WBRReport</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3073,6 +3476,11 @@
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>0% (0/19)</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\amazon-dsp-api\us\DSP Web API\WBRV2</t>
         </is>
       </c>
     </row>
